--- a/tests/fixtures/09_sales_by_region/data-export-control.xlsx
+++ b/tests/fixtures/09_sales_by_region/data-export-control.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -539,345 +539,346 @@
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>sale.product</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>sale.units</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>sale.revenue</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>sale.target</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Laptop Pro</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>320</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>384000</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>400000</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Tablet Air</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>210</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F6" s="6" t="n">
         <v>147000</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>150000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Phone X</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>450</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>225000</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>250000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="n"/>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="8" t="n">
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n">
         <v>756000</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G8" s="8" t="n">
         <v>800000</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>sale.product</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>sale.units</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>sale.revenue</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>sale.target</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Laptop Pro</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>510</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>612000</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>600000</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="7" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Tablet Air</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E12" s="6" t="n">
         <v>380</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F12" s="6" t="n">
         <v>266000</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G12" s="6" t="n">
         <v>250000</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n">
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n">
         <v>878000</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G13" s="8" t="n">
         <v>850000</v>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>sale.product</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>sale.units</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>sale.revenue</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>sale.target</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Laptop Pro</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E16" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <v>348000</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>350000</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Phone X</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>820</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F17" s="6" t="n">
         <v>410000</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>400000</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Smart Watch</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E18" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F18" s="4" t="n">
         <v>180000</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>200000</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="9" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n">
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n">
         <v>938000</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G19" s="8" t="n">
         <v>950000</v>
       </c>
     </row>
